--- a/runac/demo/DISP_SCP_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/DISP_SCP_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,13 +39,18 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="007A3B00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBEEE1"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,24 +109,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1115,363 +1128,369 @@
     <col width="40" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ATENCIÓN: en las columnas con lista desplegable sólo se admiten los valores de la lista.</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Listado de dispositivos de modalidad de cuidado residencial. MODELO PARA COMPLETAR Y ADJUNTAR</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Listado de dispositivos de modalidad de cuidado residencial</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Datos institucionales</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>El establecimiento cuenta con...</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Cuenta con PROTOCOLO ...</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Capacidad /cobertura</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Perfiles poblacionales admitidos</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>Personal del dispositivo: CANTIDAD DE PERSONAS</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>CAPACITACIONES RECIBIDAS POR EL PERSONAL QUE TRABAJA EN EL DISPOSITIVO EN EL ÚLTIMO AÑO</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>SOBRE EL PROYECTO DE RESTITUCIÓN DE DERECHOS</t>
         </is>
       </c>
-      <c r="BA3" s="2" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <t>INSERCIÓN FAMILIAR Y COMUNITARIA</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Nombre del dispositvo *</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Dependencia institucional</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Tipo de gestión</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>¿Tiene convenio con el OPN? (Solo para los de gestión no gubernamental y gestión mixta)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Localidad</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Código postal</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>El dispositivo, ¿registra las intervenciones en el Sistema Nominal digital del OPN provincial?</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>... Proyecto institucional?</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>…reglamento de convivencia?</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>... habilitación municipal?</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>... con rampas o condiciones para el acceso y circulación de personas con discapacidad</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>... tablets o computadoras para los NyA alojados en el dispositivo</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>... WIFI en el dispositivo</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>... para el ingreso del NyA al dispositivo</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>…para el abordaje de conflictos o violencia entre NyA</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>... para el abordaje de crisis y urgencias en salud mental</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>Cantidad de NyA que es posible alojar por dormitorio</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Género admitido</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>grupos de hermanos?</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>NyA dolescentes con discapacidad</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>NyA con padecimiento de salud mental</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>NyA con uso o abuso de sustancias</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>Adolescentes con hijos</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>Aloja niños de 0 a 5 años</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>Aloja niños de 6 a 12 años</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>Aloja población de 13 a 17 años</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>Aloja población de 18 años y más</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>… que conforman el equipo técnico</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AG4" s="5" t="inlineStr">
         <is>
           <t>... destinadas al cuidado del NyA</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
+      <c r="AH4" s="5" t="inlineStr">
         <is>
           <t>... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)</t>
         </is>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AI4" s="5" t="inlineStr">
         <is>
           <t>… del equipo de conducción</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr">
+      <c r="AJ4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en PROMOCION DE CUIDADOS</t>
         </is>
       </c>
-      <c r="AK4" s="4" t="inlineStr">
+      <c r="AK4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en ALIMENTACION SALUDABLE</t>
         </is>
       </c>
-      <c r="AL4" s="4" t="inlineStr">
+      <c r="AL4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en REANIMACION CARDIOPULMONAR</t>
         </is>
       </c>
-      <c r="AM4" s="4" t="inlineStr">
+      <c r="AM4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en PRIMEROS AUXILIOS</t>
         </is>
       </c>
-      <c r="AN4" s="4" t="inlineStr">
+      <c r="AN4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en ABUSO SEXUAL INFANTIL /JUVENIL</t>
         </is>
       </c>
-      <c r="AO4" s="4" t="inlineStr">
+      <c r="AO4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en PARADIGMA DE PROTECCION INTEGRAL</t>
         </is>
       </c>
-      <c r="AP4" s="4" t="inlineStr">
+      <c r="AP4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en AUTONOMIA PROGRESIVA</t>
         </is>
       </c>
-      <c r="AQ4" s="4" t="inlineStr">
+      <c r="AQ4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en ABORDAJE EN SALUD MENTAL</t>
         </is>
       </c>
-      <c r="AR4" s="4" t="inlineStr">
+      <c r="AR4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en CONSUMOS PROBLEMATICOS</t>
         </is>
       </c>
-      <c r="AS4" s="4" t="inlineStr">
+      <c r="AS4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en CULTURA DIGITAL</t>
         </is>
       </c>
-      <c r="AT4" s="4" t="inlineStr">
+      <c r="AT4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en DISCAPACIDAD</t>
         </is>
       </c>
-      <c r="AU4" s="4" t="inlineStr">
+      <c r="AU4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en ADMINISTRACION FINANCIERA</t>
         </is>
       </c>
-      <c r="AV4" s="4" t="inlineStr">
+      <c r="AV4" s="5" t="inlineStr">
         <is>
           <t>Recibió capacitación en OTRAS TEMÁTICAS</t>
         </is>
       </c>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AW4" s="5" t="inlineStr">
         <is>
           <t>Otras temáticas. Especifique</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr">
+      <c r="AX4" s="5" t="inlineStr">
         <is>
           <t>El dipositivo participa en la formulación del proyecto de restitución de derechos</t>
         </is>
       </c>
-      <c r="AY4" s="4" t="inlineStr">
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>Participa el NyA en el proyecto de restitución de derechos (PER)</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="inlineStr">
+      <c r="AZ4" s="5" t="inlineStr">
         <is>
           <t>Existe articulación entre el PER y el plan de estadía?</t>
         </is>
       </c>
-      <c r="BA4" s="4" t="inlineStr">
+      <c r="BA4" s="5" t="inlineStr">
         <is>
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de redes, mails, cartas?</t>
         </is>
       </c>
-      <c r="BB4" s="4" t="inlineStr">
+      <c r="BB4" s="5" t="inlineStr">
         <is>
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de encuentros fuera del dispositivo?</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="BC4" s="5" t="inlineStr">
         <is>
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de visitas presenciales?</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr">
+      <c r="BD4" s="5" t="inlineStr">
         <is>
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de llamadas y videollamadas?</t>
         </is>
       </c>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BE4" s="5" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr">
+      <c r="BF4" s="5" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades ARTISTICAS?</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BG4" s="5" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades DEPORTIVAS?</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr">
+      <c r="BH4" s="5" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades RECREATIVAS?</t>
         </is>
       </c>
-      <c r="BI4" s="4" t="inlineStr">
+      <c r="BI4" s="5" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan OTRAS Actividades?</t>
         </is>
@@ -1573,7 +1592,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="T5" s="6" t="n">
         <v>18</v>
       </c>
       <c r="U5" t="inlineStr">
@@ -1874,7 +1893,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T6" s="6" t="n">
         <v>13</v>
       </c>
       <c r="U6" t="inlineStr">
@@ -2179,7 +2198,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="T7" s="5" t="n">
+      <c r="T7" s="6" t="n">
         <v>2008</v>
       </c>
       <c r="U7" t="inlineStr">
@@ -2480,7 +2499,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="T8" s="6" t="n">
         <v>17</v>
       </c>
       <c r="U8" t="inlineStr">
@@ -2781,7 +2800,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="T9" s="5" t="n">
+      <c r="T9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr">
@@ -3082,7 +3101,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="T10" s="6" t="n">
         <v>827</v>
       </c>
       <c r="U10" t="inlineStr">
@@ -3383,7 +3402,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="T11" s="5" t="n">
+      <c r="T11" s="6" t="n">
         <v>2</v>
       </c>
       <c r="U11" t="inlineStr">
@@ -3688,7 +3707,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="T12" s="5" t="n">
+      <c r="T12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="U12" t="inlineStr">
@@ -3993,7 +4012,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="T13" s="5" t="n">
+      <c r="T13" s="6" t="n">
         <v>2007</v>
       </c>
       <c r="U13" t="inlineStr">
@@ -4298,7 +4317,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="T14" s="5" t="n">
+      <c r="T14" s="6" t="n">
         <v>5</v>
       </c>
       <c r="U14" t="inlineStr">
@@ -4599,7 +4618,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="T15" s="5" t="n">
+      <c r="T15" s="6" t="n">
         <v>25</v>
       </c>
       <c r="U15" t="inlineStr">
@@ -4900,7 +4919,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="T16" s="5" t="n">
+      <c r="T16" s="6" t="n">
         <v>888</v>
       </c>
       <c r="U16" t="inlineStr">
@@ -5201,7 +5220,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="T17" s="5" t="n">
+      <c r="T17" s="6" t="n">
         <v>24</v>
       </c>
       <c r="U17" t="inlineStr">
@@ -5502,7 +5521,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="T18" s="5" t="n">
+      <c r="T18" s="6" t="n">
         <v>5</v>
       </c>
       <c r="U18" t="inlineStr">
@@ -5803,7 +5822,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="T19" s="5" t="n">
+      <c r="T19" s="6" t="n">
         <v>2007</v>
       </c>
       <c r="U19" t="inlineStr">
@@ -6108,7 +6127,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="T20" s="5" t="n">
+      <c r="T20" s="6" t="n">
         <v>7</v>
       </c>
       <c r="U20" t="inlineStr">
@@ -6409,7 +6428,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="T21" s="5" t="n">
+      <c r="T21" s="6" t="n">
         <v>15</v>
       </c>
       <c r="U21" t="inlineStr">
@@ -6714,7 +6733,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="T22" s="5" t="n">
+      <c r="T22" s="6" t="n">
         <v>221</v>
       </c>
       <c r="U22" t="inlineStr">
@@ -7019,7 +7038,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="T23" s="5" t="n">
+      <c r="T23" s="6" t="n">
         <v>24</v>
       </c>
       <c r="U23" t="inlineStr">
@@ -7324,7 +7343,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="T24" s="5" t="n">
+      <c r="T24" s="6" t="n">
         <v>13</v>
       </c>
       <c r="U24" t="inlineStr">
@@ -7629,7 +7648,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="T25" s="5" t="n">
+      <c r="T25" s="6" t="n">
         <v>2002</v>
       </c>
       <c r="U25" t="inlineStr">
@@ -7930,7 +7949,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="T26" s="5" t="n">
+      <c r="T26" s="6" t="n">
         <v>17</v>
       </c>
       <c r="U26" t="inlineStr">
@@ -8235,7 +8254,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="T27" s="5" t="n">
+      <c r="T27" s="6" t="n">
         <v>9</v>
       </c>
       <c r="U27" t="inlineStr">
@@ -8536,7 +8555,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="T28" s="5" t="n">
+      <c r="T28" s="6" t="n">
         <v>217</v>
       </c>
       <c r="U28" t="inlineStr">
@@ -8841,7 +8860,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="T29" s="5" t="n">
+      <c r="T29" s="6" t="n">
         <v>4</v>
       </c>
       <c r="U29" t="inlineStr">
@@ -9146,7 +9165,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="T30" s="5" t="n">
+      <c r="T30" s="6" t="n">
         <v>20</v>
       </c>
       <c r="U30" t="inlineStr">
@@ -9447,7 +9466,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="T31" s="5" t="n">
+      <c r="T31" s="6" t="n">
         <v>623</v>
       </c>
       <c r="U31" t="inlineStr">
@@ -9752,7 +9771,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="T32" s="5" t="n">
+      <c r="T32" s="6" t="n">
         <v>17</v>
       </c>
       <c r="U32" t="inlineStr">
@@ -10053,7 +10072,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="T33" s="5" t="n">
+      <c r="T33" s="6" t="n">
         <v>8</v>
       </c>
       <c r="U33" t="inlineStr">
@@ -10354,7 +10373,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="T34" s="5" t="n">
+      <c r="T34" s="6" t="n">
         <v>2006</v>
       </c>
       <c r="U34" t="inlineStr">
@@ -10560,521 +10579,522 @@
       </c>
     </row>
     <row r="35">
-      <c r="T35" s="5" t="n"/>
+      <c r="T35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="T36" s="5" t="n"/>
+      <c r="T36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="T37" s="5" t="n"/>
+      <c r="T37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="T38" s="5" t="n"/>
+      <c r="T38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="T39" s="5" t="n"/>
+      <c r="T39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="T40" s="5" t="n"/>
+      <c r="T40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="T41" s="5" t="n"/>
+      <c r="T41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="T42" s="5" t="n"/>
+      <c r="T42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="T43" s="5" t="n"/>
+      <c r="T43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="T44" s="5" t="n"/>
+      <c r="T44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="T45" s="5" t="n"/>
+      <c r="T45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="T46" s="5" t="n"/>
+      <c r="T46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="T47" s="5" t="n"/>
+      <c r="T47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="T48" s="5" t="n"/>
+      <c r="T48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="T49" s="5" t="n"/>
+      <c r="T49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="T50" s="5" t="n"/>
+      <c r="T50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="T51" s="5" t="n"/>
+      <c r="T51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="T52" s="5" t="n"/>
+      <c r="T52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="T53" s="5" t="n"/>
+      <c r="T53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="T54" s="5" t="n"/>
+      <c r="T54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="T55" s="5" t="n"/>
+      <c r="T55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="T56" s="5" t="n"/>
+      <c r="T56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="T57" s="5" t="n"/>
+      <c r="T57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="T58" s="5" t="n"/>
+      <c r="T58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="T59" s="5" t="n"/>
+      <c r="T59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="T60" s="5" t="n"/>
+      <c r="T60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="T61" s="5" t="n"/>
+      <c r="T61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="T62" s="5" t="n"/>
+      <c r="T62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="T63" s="5" t="n"/>
+      <c r="T63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="T64" s="5" t="n"/>
+      <c r="T64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="T65" s="5" t="n"/>
+      <c r="T65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="T66" s="5" t="n"/>
+      <c r="T66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="T67" s="5" t="n"/>
+      <c r="T67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="T68" s="5" t="n"/>
+      <c r="T68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="T69" s="5" t="n"/>
+      <c r="T69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="T70" s="5" t="n"/>
+      <c r="T70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="T71" s="5" t="n"/>
+      <c r="T71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="T72" s="5" t="n"/>
+      <c r="T72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="T73" s="5" t="n"/>
+      <c r="T73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="T74" s="5" t="n"/>
+      <c r="T74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="T75" s="5" t="n"/>
+      <c r="T75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="T76" s="5" t="n"/>
+      <c r="T76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="T77" s="5" t="n"/>
+      <c r="T77" s="6" t="n"/>
     </row>
     <row r="78">
-      <c r="T78" s="5" t="n"/>
+      <c r="T78" s="6" t="n"/>
     </row>
     <row r="79">
-      <c r="T79" s="5" t="n"/>
+      <c r="T79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="T80" s="5" t="n"/>
+      <c r="T80" s="6" t="n"/>
     </row>
     <row r="81">
-      <c r="T81" s="5" t="n"/>
+      <c r="T81" s="6" t="n"/>
     </row>
     <row r="82">
-      <c r="T82" s="5" t="n"/>
+      <c r="T82" s="6" t="n"/>
     </row>
     <row r="83">
-      <c r="T83" s="5" t="n"/>
+      <c r="T83" s="6" t="n"/>
     </row>
     <row r="84">
-      <c r="T84" s="5" t="n"/>
+      <c r="T84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="T85" s="5" t="n"/>
+      <c r="T85" s="6" t="n"/>
     </row>
     <row r="86">
-      <c r="T86" s="5" t="n"/>
+      <c r="T86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="T87" s="5" t="n"/>
+      <c r="T87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="T88" s="5" t="n"/>
+      <c r="T88" s="6" t="n"/>
     </row>
     <row r="89">
-      <c r="T89" s="5" t="n"/>
+      <c r="T89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="T90" s="5" t="n"/>
+      <c r="T90" s="6" t="n"/>
     </row>
     <row r="91">
-      <c r="T91" s="5" t="n"/>
+      <c r="T91" s="6" t="n"/>
     </row>
     <row r="92">
-      <c r="T92" s="5" t="n"/>
+      <c r="T92" s="6" t="n"/>
     </row>
     <row r="93">
-      <c r="T93" s="5" t="n"/>
+      <c r="T93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="T94" s="5" t="n"/>
+      <c r="T94" s="6" t="n"/>
     </row>
     <row r="95">
-      <c r="T95" s="5" t="n"/>
+      <c r="T95" s="6" t="n"/>
     </row>
     <row r="96">
-      <c r="T96" s="5" t="n"/>
+      <c r="T96" s="6" t="n"/>
     </row>
     <row r="97">
-      <c r="T97" s="5" t="n"/>
+      <c r="T97" s="6" t="n"/>
     </row>
     <row r="98">
-      <c r="T98" s="5" t="n"/>
+      <c r="T98" s="6" t="n"/>
     </row>
     <row r="99">
-      <c r="T99" s="5" t="n"/>
+      <c r="T99" s="6" t="n"/>
     </row>
     <row r="100">
-      <c r="T100" s="5" t="n"/>
+      <c r="T100" s="6" t="n"/>
     </row>
     <row r="101">
-      <c r="T101" s="5" t="n"/>
+      <c r="T101" s="6" t="n"/>
     </row>
     <row r="102">
-      <c r="T102" s="5" t="n"/>
+      <c r="T102" s="6" t="n"/>
     </row>
     <row r="103">
-      <c r="T103" s="5" t="n"/>
+      <c r="T103" s="6" t="n"/>
     </row>
     <row r="104">
-      <c r="T104" s="5" t="n"/>
+      <c r="T104" s="6" t="n"/>
     </row>
     <row r="105">
-      <c r="T105" s="5" t="n"/>
+      <c r="T105" s="6" t="n"/>
     </row>
     <row r="106">
-      <c r="T106" s="5" t="n"/>
+      <c r="T106" s="6" t="n"/>
     </row>
     <row r="107">
-      <c r="T107" s="5" t="n"/>
+      <c r="T107" s="6" t="n"/>
     </row>
     <row r="108">
-      <c r="T108" s="5" t="n"/>
+      <c r="T108" s="6" t="n"/>
     </row>
     <row r="109">
-      <c r="T109" s="5" t="n"/>
+      <c r="T109" s="6" t="n"/>
     </row>
     <row r="110">
-      <c r="T110" s="5" t="n"/>
+      <c r="T110" s="6" t="n"/>
     </row>
     <row r="111">
-      <c r="T111" s="5" t="n"/>
+      <c r="T111" s="6" t="n"/>
     </row>
     <row r="112">
-      <c r="T112" s="5" t="n"/>
+      <c r="T112" s="6" t="n"/>
     </row>
     <row r="113">
-      <c r="T113" s="5" t="n"/>
+      <c r="T113" s="6" t="n"/>
     </row>
     <row r="114">
-      <c r="T114" s="5" t="n"/>
+      <c r="T114" s="6" t="n"/>
     </row>
     <row r="115">
-      <c r="T115" s="5" t="n"/>
+      <c r="T115" s="6" t="n"/>
     </row>
     <row r="116">
-      <c r="T116" s="5" t="n"/>
+      <c r="T116" s="6" t="n"/>
     </row>
     <row r="117">
-      <c r="T117" s="5" t="n"/>
+      <c r="T117" s="6" t="n"/>
     </row>
     <row r="118">
-      <c r="T118" s="5" t="n"/>
+      <c r="T118" s="6" t="n"/>
     </row>
     <row r="119">
-      <c r="T119" s="5" t="n"/>
+      <c r="T119" s="6" t="n"/>
     </row>
     <row r="120">
-      <c r="T120" s="5" t="n"/>
+      <c r="T120" s="6" t="n"/>
     </row>
     <row r="121">
-      <c r="T121" s="5" t="n"/>
+      <c r="T121" s="6" t="n"/>
     </row>
     <row r="122">
-      <c r="T122" s="5" t="n"/>
+      <c r="T122" s="6" t="n"/>
     </row>
     <row r="123">
-      <c r="T123" s="5" t="n"/>
+      <c r="T123" s="6" t="n"/>
     </row>
     <row r="124">
-      <c r="T124" s="5" t="n"/>
+      <c r="T124" s="6" t="n"/>
     </row>
     <row r="125">
-      <c r="T125" s="5" t="n"/>
+      <c r="T125" s="6" t="n"/>
     </row>
     <row r="126">
-      <c r="T126" s="5" t="n"/>
+      <c r="T126" s="6" t="n"/>
     </row>
     <row r="127">
-      <c r="T127" s="5" t="n"/>
+      <c r="T127" s="6" t="n"/>
     </row>
     <row r="128">
-      <c r="T128" s="5" t="n"/>
+      <c r="T128" s="6" t="n"/>
     </row>
     <row r="129">
-      <c r="T129" s="5" t="n"/>
+      <c r="T129" s="6" t="n"/>
     </row>
     <row r="130">
-      <c r="T130" s="5" t="n"/>
+      <c r="T130" s="6" t="n"/>
     </row>
     <row r="131">
-      <c r="T131" s="5" t="n"/>
+      <c r="T131" s="6" t="n"/>
     </row>
     <row r="132">
-      <c r="T132" s="5" t="n"/>
+      <c r="T132" s="6" t="n"/>
     </row>
     <row r="133">
-      <c r="T133" s="5" t="n"/>
+      <c r="T133" s="6" t="n"/>
     </row>
     <row r="134">
-      <c r="T134" s="5" t="n"/>
+      <c r="T134" s="6" t="n"/>
     </row>
     <row r="135">
-      <c r="T135" s="5" t="n"/>
+      <c r="T135" s="6" t="n"/>
     </row>
     <row r="136">
-      <c r="T136" s="5" t="n"/>
+      <c r="T136" s="6" t="n"/>
     </row>
     <row r="137">
-      <c r="T137" s="5" t="n"/>
+      <c r="T137" s="6" t="n"/>
     </row>
     <row r="138">
-      <c r="T138" s="5" t="n"/>
+      <c r="T138" s="6" t="n"/>
     </row>
     <row r="139">
-      <c r="T139" s="5" t="n"/>
+      <c r="T139" s="6" t="n"/>
     </row>
     <row r="140">
-      <c r="T140" s="5" t="n"/>
+      <c r="T140" s="6" t="n"/>
     </row>
     <row r="141">
-      <c r="T141" s="5" t="n"/>
+      <c r="T141" s="6" t="n"/>
     </row>
     <row r="142">
-      <c r="T142" s="5" t="n"/>
+      <c r="T142" s="6" t="n"/>
     </row>
     <row r="143">
-      <c r="T143" s="5" t="n"/>
+      <c r="T143" s="6" t="n"/>
     </row>
     <row r="144">
-      <c r="T144" s="5" t="n"/>
+      <c r="T144" s="6" t="n"/>
     </row>
     <row r="145">
-      <c r="T145" s="5" t="n"/>
+      <c r="T145" s="6" t="n"/>
     </row>
     <row r="146">
-      <c r="T146" s="5" t="n"/>
+      <c r="T146" s="6" t="n"/>
     </row>
     <row r="147">
-      <c r="T147" s="5" t="n"/>
+      <c r="T147" s="6" t="n"/>
     </row>
     <row r="148">
-      <c r="T148" s="5" t="n"/>
+      <c r="T148" s="6" t="n"/>
     </row>
     <row r="149">
-      <c r="T149" s="5" t="n"/>
+      <c r="T149" s="6" t="n"/>
     </row>
     <row r="150">
-      <c r="T150" s="5" t="n"/>
+      <c r="T150" s="6" t="n"/>
     </row>
     <row r="151">
-      <c r="T151" s="5" t="n"/>
+      <c r="T151" s="6" t="n"/>
     </row>
     <row r="152">
-      <c r="T152" s="5" t="n"/>
+      <c r="T152" s="6" t="n"/>
     </row>
     <row r="153">
-      <c r="T153" s="5" t="n"/>
+      <c r="T153" s="6" t="n"/>
     </row>
     <row r="154">
-      <c r="T154" s="5" t="n"/>
+      <c r="T154" s="6" t="n"/>
     </row>
     <row r="155">
-      <c r="T155" s="5" t="n"/>
+      <c r="T155" s="6" t="n"/>
     </row>
     <row r="156">
-      <c r="T156" s="5" t="n"/>
+      <c r="T156" s="6" t="n"/>
     </row>
     <row r="157">
-      <c r="T157" s="5" t="n"/>
+      <c r="T157" s="6" t="n"/>
     </row>
     <row r="158">
-      <c r="T158" s="5" t="n"/>
+      <c r="T158" s="6" t="n"/>
     </row>
     <row r="159">
-      <c r="T159" s="5" t="n"/>
+      <c r="T159" s="6" t="n"/>
     </row>
     <row r="160">
-      <c r="T160" s="5" t="n"/>
+      <c r="T160" s="6" t="n"/>
     </row>
     <row r="161">
-      <c r="T161" s="5" t="n"/>
+      <c r="T161" s="6" t="n"/>
     </row>
     <row r="162">
-      <c r="T162" s="5" t="n"/>
+      <c r="T162" s="6" t="n"/>
     </row>
     <row r="163">
-      <c r="T163" s="5" t="n"/>
+      <c r="T163" s="6" t="n"/>
     </row>
     <row r="164">
-      <c r="T164" s="5" t="n"/>
+      <c r="T164" s="6" t="n"/>
     </row>
     <row r="165">
-      <c r="T165" s="5" t="n"/>
+      <c r="T165" s="6" t="n"/>
     </row>
     <row r="166">
-      <c r="T166" s="5" t="n"/>
+      <c r="T166" s="6" t="n"/>
     </row>
     <row r="167">
-      <c r="T167" s="5" t="n"/>
+      <c r="T167" s="6" t="n"/>
     </row>
     <row r="168">
-      <c r="T168" s="5" t="n"/>
+      <c r="T168" s="6" t="n"/>
     </row>
     <row r="169">
-      <c r="T169" s="5" t="n"/>
+      <c r="T169" s="6" t="n"/>
     </row>
     <row r="170">
-      <c r="T170" s="5" t="n"/>
+      <c r="T170" s="6" t="n"/>
     </row>
     <row r="171">
-      <c r="T171" s="5" t="n"/>
+      <c r="T171" s="6" t="n"/>
     </row>
     <row r="172">
-      <c r="T172" s="5" t="n"/>
+      <c r="T172" s="6" t="n"/>
     </row>
     <row r="173">
-      <c r="T173" s="5" t="n"/>
+      <c r="T173" s="6" t="n"/>
     </row>
     <row r="174">
-      <c r="T174" s="5" t="n"/>
+      <c r="T174" s="6" t="n"/>
     </row>
     <row r="175">
-      <c r="T175" s="5" t="n"/>
+      <c r="T175" s="6" t="n"/>
     </row>
     <row r="176">
-      <c r="T176" s="5" t="n"/>
+      <c r="T176" s="6" t="n"/>
     </row>
     <row r="177">
-      <c r="T177" s="5" t="n"/>
+      <c r="T177" s="6" t="n"/>
     </row>
     <row r="178">
-      <c r="T178" s="5" t="n"/>
+      <c r="T178" s="6" t="n"/>
     </row>
     <row r="179">
-      <c r="T179" s="5" t="n"/>
+      <c r="T179" s="6" t="n"/>
     </row>
     <row r="180">
-      <c r="T180" s="5" t="n"/>
+      <c r="T180" s="6" t="n"/>
     </row>
     <row r="181">
-      <c r="T181" s="5" t="n"/>
+      <c r="T181" s="6" t="n"/>
     </row>
     <row r="182">
-      <c r="T182" s="5" t="n"/>
+      <c r="T182" s="6" t="n"/>
     </row>
     <row r="183">
-      <c r="T183" s="5" t="n"/>
+      <c r="T183" s="6" t="n"/>
     </row>
     <row r="184">
-      <c r="T184" s="5" t="n"/>
+      <c r="T184" s="6" t="n"/>
     </row>
     <row r="185">
-      <c r="T185" s="5" t="n"/>
+      <c r="T185" s="6" t="n"/>
     </row>
     <row r="186">
-      <c r="T186" s="5" t="n"/>
+      <c r="T186" s="6" t="n"/>
     </row>
     <row r="187">
-      <c r="T187" s="5" t="n"/>
+      <c r="T187" s="6" t="n"/>
     </row>
     <row r="188">
-      <c r="T188" s="5" t="n"/>
+      <c r="T188" s="6" t="n"/>
     </row>
     <row r="189">
-      <c r="T189" s="5" t="n"/>
+      <c r="T189" s="6" t="n"/>
     </row>
     <row r="190">
-      <c r="T190" s="5" t="n"/>
+      <c r="T190" s="6" t="n"/>
     </row>
     <row r="191">
-      <c r="T191" s="5" t="n"/>
+      <c r="T191" s="6" t="n"/>
     </row>
     <row r="192">
-      <c r="T192" s="5" t="n"/>
+      <c r="T192" s="6" t="n"/>
     </row>
     <row r="193">
-      <c r="T193" s="5" t="n"/>
+      <c r="T193" s="6" t="n"/>
     </row>
     <row r="194">
-      <c r="T194" s="5" t="n"/>
+      <c r="T194" s="6" t="n"/>
     </row>
     <row r="195">
-      <c r="T195" s="5" t="n"/>
+      <c r="T195" s="6" t="n"/>
     </row>
     <row r="196">
-      <c r="T196" s="5" t="n"/>
+      <c r="T196" s="6" t="n"/>
     </row>
     <row r="197">
-      <c r="T197" s="5" t="n"/>
+      <c r="T197" s="6" t="n"/>
     </row>
     <row r="198">
-      <c r="T198" s="5" t="n"/>
+      <c r="T198" s="6" t="n"/>
     </row>
     <row r="199">
-      <c r="T199" s="5" t="n"/>
+      <c r="T199" s="6" t="n"/>
     </row>
     <row r="200">
-      <c r="T200" s="5" t="n"/>
+      <c r="T200" s="6" t="n"/>
     </row>
     <row r="201">
-      <c r="T201" s="5" t="n"/>
+      <c r="T201" s="6" t="n"/>
     </row>
     <row r="202">
-      <c r="T202" s="5" t="n"/>
+      <c r="T202" s="6" t="n"/>
     </row>
     <row r="203">
-      <c r="T203" s="5" t="n"/>
+      <c r="T203" s="6" t="n"/>
     </row>
     <row r="204">
-      <c r="T204" s="5" t="n"/>
+      <c r="T204" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="BA3:BI3"/>
+    <mergeCell ref="A1:BI1"/>
+    <mergeCell ref="AJ3:AW3"/>
     <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="AJ3:AW3"/>
     <mergeCell ref="V3:AE3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="AX3:AZ3"/>
@@ -11259,26 +11279,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Indicación para el llenado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Hoja: M Residencial</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Datos institucionales</t>
         </is>
@@ -11290,7 +11310,7 @@
           <t>Nombre del dispositvo</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Campo obligatorio.</t>
         </is>
@@ -11302,7 +11322,7 @@
           <t>Dependencia institucional</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Organismo, ministerio, secretaría, dirección o área estatal de la cual depende orgánica y formalmente el dispositivo de cuidado.</t>
         </is>
@@ -11314,7 +11334,7 @@
           <t>Tipo de gestión</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Carácter público o privado/asociativo de la administración de la institución de cuidado alternativo.
 Debe elegirse un valor de la lista "Tipo de gestión".</t>
@@ -11327,7 +11347,7 @@
           <t>¿Tiene convenio con el OPN? (Solo para los de gestión no gubernamental y gestión mixta)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11339,7 +11359,7 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Ciudad, municipio, comuna o localidad geográfica donde se encuentra el dispositivo físicamente.</t>
         </is>
@@ -11351,7 +11371,7 @@
           <t>Dirección</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Domicilio real (calle, número, piso/departamento, entre calles) donde se encuentra ubicada la residencia.</t>
         </is>
@@ -11363,7 +11383,7 @@
           <t>Código postal</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Código Postal Argentino de la localidad correspondiente.</t>
         </is>
@@ -11375,7 +11395,7 @@
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Número de contacto telefónico institucional o celular de guardia de la residencia.</t>
         </is>
@@ -11387,14 +11407,14 @@
           <t>El dispositivo, ¿registra las intervenciones en el Sistema Nominal digital del OPN provincial?</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>El establecimiento cuenta con...</t>
         </is>
@@ -11406,7 +11426,7 @@
           <t>... Proyecto institucional?</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "... Proyecto institucional?".</t>
         </is>
@@ -11418,7 +11438,7 @@
           <t>…reglamento de convivencia?</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "... Proyecto institucional?".</t>
         </is>
@@ -11430,7 +11450,7 @@
           <t>... habilitación municipal?</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "habilitación municipal?".</t>
         </is>
@@ -11442,7 +11462,7 @@
           <t>... con rampas o condiciones para el acceso y circulación de personas con discapacidad</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "... con rampas o condiciones para el acceso y circulación de personas con discapacidad".</t>
         </is>
@@ -11454,7 +11474,7 @@
           <t>... tablets o computadoras para los NyA alojados en el dispositivo</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista ". tablets o computadoras para los NyA alojados en el dispositivo".</t>
         </is>
@@ -11466,14 +11486,14 @@
           <t>... WIFI en el dispositivo</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Cuenta con PROTOCOLO ...</t>
         </is>
@@ -11485,7 +11505,7 @@
           <t>... para el ingreso del NyA al dispositivo</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11497,7 +11517,7 @@
           <t>…para el abordaje de conflictos o violencia entre NyA</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11509,14 +11529,14 @@
           <t>... para el abordaje de crisis y urgencias en salud mental</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Capacidad /cobertura</t>
         </is>
@@ -11528,7 +11548,7 @@
           <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Cantidad máxima total de plazas (camas) habilitadas formalmente por el dispositivo para el alojamiento de NyA.</t>
         </is>
@@ -11540,7 +11560,7 @@
           <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
+      <c r="B26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11548,7 +11568,7 @@
           <t>Cantidad de NyA que es posible alojar por dormitorio</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Distribución edilicia por habitación. Indicar cuántas camas hay en promedio por dormitorio.
 Debe elegirse un valor de la lista "Cantidad de NyA que es posible alojar por dormitorio".</t>
@@ -11556,7 +11576,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Perfiles poblacionales admitidos</t>
         </is>
@@ -11568,7 +11588,7 @@
           <t>Género admitido</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Perfil de género de la población de NyA que tiene autorización de ingreso al dispositivo.
 Debe elegirse un valor de la lista "Género admitido".</t>
@@ -11581,7 +11601,7 @@
           <t>grupos de hermanos?</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11593,7 +11613,7 @@
           <t>NyA dolescentes con discapacidad</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11605,7 +11625,7 @@
           <t>NyA con padecimiento de salud mental</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11617,7 +11637,7 @@
           <t>NyA con uso o abuso de sustancias</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11629,7 +11649,7 @@
           <t>Adolescentes con hijos</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11641,7 +11661,7 @@
           <t>Aloja niños de 0 a 5 años</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Indica si el dispositivo admite y aloja a niños en la primera infancia (0 a 5 años inclusive).
 Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
@@ -11654,7 +11674,7 @@
           <t>Aloja niños de 6 a 12 años</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Indica si el dispositivo admite y aloja a niños en edad escolar primaria (6 a 12 años inclusive).
 Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
@@ -11667,7 +11687,7 @@
           <t>Aloja población de 13 a 17 años</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Indica si el dispositivo admite y aloja a adolescentes de 13 a 17 años inclusive.
 Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
@@ -11680,7 +11700,7 @@
           <t>Aloja población de 18 años y más</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Indica si excepcionalmente aloja a jóvenes de 18 años o más que continúan en tránsito de egreso o bajo prórroga legal de protección.
 Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
@@ -11688,7 +11708,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Personal del dispositivo: CANTIDAD DE PERSONAS</t>
         </is>
@@ -11700,7 +11720,7 @@
           <t>… que conforman el equipo técnico</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "… que conforman el equipo técnico".</t>
         </is>
@@ -11712,7 +11732,7 @@
           <t>... destinadas al cuidado del NyA</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "... destinadas al cuidado del NyA".</t>
         </is>
@@ -11724,7 +11744,7 @@
           <t>... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)".</t>
         </is>
@@ -11736,14 +11756,14 @@
           <t>… del equipo de conducción</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "del equipo de conducción".</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>CAPACITACIONES RECIBIDAS POR EL PERSONAL QUE TRABAJA EN EL DISPOSITIVO EN EL ÚLTIMO AÑO</t>
         </is>
@@ -11755,7 +11775,7 @@
           <t>Recibió capacitación en PROMOCION DE CUIDADOS</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11767,7 +11787,7 @@
           <t>Recibió capacitación en ALIMENTACION SALUDABLE</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11779,7 +11799,7 @@
           <t>Recibió capacitación en REANIMACION CARDIOPULMONAR</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11791,7 +11811,7 @@
           <t>Recibió capacitación en PRIMEROS AUXILIOS</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11803,7 +11823,7 @@
           <t>Recibió capacitación en ABUSO SEXUAL INFANTIL /JUVENIL</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11815,7 +11835,7 @@
           <t>Recibió capacitación en PARADIGMA DE PROTECCION INTEGRAL</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11827,7 +11847,7 @@
           <t>Recibió capacitación en AUTONOMIA PROGRESIVA</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11839,7 +11859,7 @@
           <t>Recibió capacitación en ABORDAJE EN SALUD MENTAL</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11851,7 +11871,7 @@
           <t>Recibió capacitación en CONSUMOS PROBLEMATICOS</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11863,7 +11883,7 @@
           <t>Recibió capacitación en CULTURA DIGITAL</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11875,7 +11895,7 @@
           <t>Recibió capacitación en DISCAPACIDAD</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11887,7 +11907,7 @@
           <t>Recibió capacitación en ADMINISTRACION FINANCIERA</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11899,7 +11919,7 @@
           <t>Recibió capacitación en OTRAS TEMÁTICAS</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11911,14 +11931,14 @@
           <t>Otras temáticas. Especifique</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Si se marcó 'Sí' en la columna de capacitación en 'OTRAS TEMÁTICAS', especificar aquí cuáles fueron los temas abordados de forma sintética.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>SOBRE EL PROYECTO DE RESTITUCIÓN DE DERECHOS</t>
         </is>
@@ -11930,7 +11950,7 @@
           <t>El dipositivo participa en la formulación del proyecto de restitución de derechos</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "El dipositivo participa en la formulación del proyecto de restitución de derechos".</t>
         </is>
@@ -11942,7 +11962,7 @@
           <t>Participa el NyA en el proyecto de restitución de derechos (PER)</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".</t>
         </is>
@@ -11954,7 +11974,7 @@
           <t>Existe articulación entre el PER y el plan de estadía?</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>¿Las actividades cotidianas del NyA en el dispositivo están alineadas y coordinadas con el proyecto de restitución trazado por la autoridad de aplicación?
 Debe elegirse un valor de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".</t>
@@ -11962,7 +11982,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>INSERCIÓN FAMILIAR Y COMUNITARIA</t>
         </is>
@@ -11974,7 +11994,7 @@
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de redes, mails, cartas?</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11986,7 +12006,7 @@
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de encuentros fuera del dispositivo?</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -11998,7 +12018,7 @@
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de visitas presenciales?</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -12010,7 +12030,7 @@
           <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de llamadas y videollamadas?</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
         </is>
@@ -12022,7 +12042,7 @@
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
         </is>
@@ -12034,7 +12054,7 @@
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades ARTISTICAS?</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
         </is>
@@ -12046,7 +12066,7 @@
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades DEPORTIVAS?</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
         </is>
@@ -12058,7 +12078,7 @@
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades RECREATIVAS?</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
         </is>
@@ -12070,7 +12090,7 @@
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan OTRAS Actividades?</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
         </is>
@@ -12108,77 +12128,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Cantidad de NyA que es posible alojar por dormitorio</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>... con rampas o condiciones para el acceso y circulación de personas con discapacidad</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>del equipo de conducción</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>... destinadas al cuidado del NyA</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>El dipositivo participa en la formulación del proyecto de restitución de derechos</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Género admitido</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>habilitación municipal?</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Participa el NyA en el proyecto de restitución de derechos (PER)</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>... Proyecto institucional?</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>… que conforman el equipo técnico</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Sí / No / Sin datos</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>. tablets o computadoras para los NyA alojados en el dispositivo</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Tipo de gestión</t>
         </is>

--- a/runac/demo/DISP_SCP_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/DISP_SCP_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -368,8 +368,7 @@
       <text>
         <t>Capacidad de alojamiento (Plazas)
 Cantidad máxima total de plazas (camas) habilitadas formalmente por el dispositivo para el alojamiento de NyA.
-Qué se espera: texto
-Máximo 255 caracteres.
+Qué se espera: un número entero
 No es obligatorio.</t>
       </text>
     </comment>
@@ -1567,10 +1566,8 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="S4" s="5" t="n">
+        <v>52</v>
       </c>
       <c r="T4" s="5" t="n">
         <v>18</v>
@@ -1868,10 +1865,8 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="S5" s="5" t="n">
+        <v>37</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>13</v>
@@ -2173,17 +2168,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="S6" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>2008</v>
+        <v>10</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Entre 5 y 8 por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2198,7 +2191,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2208,17 +2201,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2228,27 +2221,27 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8 o más perosnas</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8 o más personas</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2258,7 +2251,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2268,7 +2261,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2283,12 +2276,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2298,53 +2291,53 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>en algunas situaciones</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>No en ninguna situación</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>en la mayoría de las situaciones</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>en algunas situaciones</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>No en ninguna situación</t>
-        </is>
-      </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,74 +2347,74 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Belgrano 1940</t>
+          <t>Belgrano 624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D6539A</t>
+          <t>Q1344J</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11-4702-4770</t>
+          <t>11-4667-4770</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2474,10 +2467,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="S7" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>17</v>
@@ -2775,10 +2766,8 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="S8" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="T8" s="5" t="n">
         <v>1</v>
@@ -2988,12 +2977,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3003,32 +2992,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rivadavia 2236</t>
+          <t>Rivadavia 1773</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>L6147D</t>
+          <t>Q4910E</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11-4371-7484</t>
+          <t>11-4505-3144</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3038,7 +3027,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3048,12 +3037,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>para algunos pocos espcios</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3063,12 +3052,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -3076,13 +3065,11 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="S9" s="5" t="n">
+        <v>827</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>827</v>
+        <v>2009</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -3091,22 +3078,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3121,17 +3108,17 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3141,17 +3128,17 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -3161,22 +3148,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -3186,7 +3173,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -3196,7 +3183,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3206,7 +3193,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -3227,7 +3214,7 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>No se realiza desde el dispositivo</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3237,17 +3224,17 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3257,49 +3244,49 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3309,22 +3296,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Alberdi 3603</t>
+          <t>San Martín 2625</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Y1158B</t>
+          <t>R1653F</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11-4177-3442</t>
+          <t>11-4315-5088</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3349,22 +3336,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>aunque se puede adaptar si lo requiere</t>
+          <t>y no es posible adaptarlos</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3374,16 +3361,14 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3397,27 +3382,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3427,37 +3412,37 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>No cuenta con equipo técnico</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3477,7 +3462,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -3492,12 +3477,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3507,7 +3492,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -3517,19 +3502,15 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
           <t>en todas las situaciones</t>
@@ -3537,22 +3518,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3562,39 +3543,39 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3609,27 +3590,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alberdi 4273</t>
+          <t>Mitre 2931</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>S9785F</t>
+          <t>Q8149J</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11-4128-2889</t>
+          <t>11-4623-2894</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3639,14 +3620,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>esta actualizado y no se aplica</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>No</t>
@@ -3659,22 +3640,22 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -3682,17 +3663,15 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="S11" s="5" t="n">
+        <v>54</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Entre 5 y 8 por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -3702,12 +3681,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3717,12 +3696,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3732,42 +3711,42 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No cuenta con equipo técnico</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>No cuena con personal de cuidado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>No cuenta con personal de apoyo</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3777,32 +3756,32 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3812,37 +3791,33 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No se realiza desde el dispositivo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -3852,12 +3827,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3872,34 +3847,34 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3914,7 +3889,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3924,17 +3899,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rivadavia 3909</t>
+          <t>San Martín 2424</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>U8244D</t>
+          <t>X6491B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11-4623-8752</t>
+          <t>11-4938-4848</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3944,14 +3919,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>esta actualizado y no se aplica</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>pero esta en diseño</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Si</t>
@@ -3959,12 +3934,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí en la mayoría de los espacios</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -3979,25 +3954,23 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>203</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>2007</v>
+        <v>201</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Hasta 4 NyA por dormitorio</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -4007,12 +3980,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -4022,42 +3995,42 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No cuena con personal de cuidado</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -4067,7 +4040,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No cuenta con personal de conducción</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -4082,7 +4055,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -4092,57 +4065,57 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Discapacidad</t>
+          <t>Acompañamiento terapéutico</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>No se realiza desde el dispositivo</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4152,52 +4125,52 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
     </row>
@@ -4214,67 +4187,67 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No gubernamental</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alberdi 2059</t>
+          <t>Mitre 2810</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>N8206B</t>
+          <t>Y8633G</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11-4830-5681</t>
+          <t>11-4163-4388</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>aunque se puede adaptar si lo requiere</t>
+          <t>Sí en todos los espacios requeridos</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -4284,7 +4257,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -4292,47 +4265,45 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="S13" s="5" t="n">
+        <v>56</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Entre 5 y 8 por dormitorio</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Aloja solo niñas y adolescentes mujeres</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -4342,37 +4313,37 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>No cuenta con equipo técnico</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -4382,7 +4353,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4392,12 +4363,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4407,12 +4378,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -4422,12 +4393,12 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -4443,19 +4414,19 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr">
         <is>
+          <t>en todas las situaciones</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
           <t>en algunas situaciones</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>en la mayoría de las situaciones</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="BA13" t="inlineStr">
         <is>
           <t>No</t>
@@ -4463,7 +4434,7 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4478,44 +4449,44 @@
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
         <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4525,22 +4496,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sarmiento 322</t>
+          <t>Güemes 770</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D8022C</t>
+          <t>W1317I</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11-4987-8564</t>
+          <t>11-4153-6733</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4550,60 +4521,58 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>pero esta en diseño</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>esta actualizado y se aplica</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí en todos los espacios requeridos</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>17</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Entre 5 y 8 por dormitorio</t>
+          <t>Hasta 4 NyA por dormitorio</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -4613,32 +4582,32 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4648,32 +4617,32 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4683,27 +4652,27 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -4713,17 +4682,17 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
@@ -4733,7 +4702,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4744,12 +4713,12 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -4759,7 +4728,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4769,17 +4738,17 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -4794,12 +4763,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
     </row>
@@ -4811,52 +4780,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>Mixta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alberdi 2089</t>
+          <t>Belgrano 3667</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>E5941J</t>
+          <t>K9548E</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-4924-2983</t>
+          <t>11-4730-9817</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4866,7 +4835,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>para algunos pocos espcios</t>
+          <t>aunque se puede adaptar si lo requiere</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -4876,17 +4845,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -4894,27 +4863,25 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="S15" s="5" t="n">
+        <v>208</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>888</v>
+        <v>643</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Hasta 4 NyA por dormitorio</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -4934,12 +4901,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -4954,47 +4921,47 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>No cuenta con equipo técnico</t>
+          <t>6 o más personas</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 o más perosnas</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 o más personas</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3 o más personas</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -5004,7 +4971,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -5014,12 +4981,12 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -5034,23 +5001,23 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -5070,7 +5037,7 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
@@ -5080,44 +5047,44 @@
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>Mixta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5127,52 +5094,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alberdi 4120</t>
+          <t>Alberdi 1616</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>U1282B</t>
+          <t>L4545H</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-4401-4630</t>
+          <t>11-4383-9595</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>esta actualizado y no se aplica</t>
+          <t>esta actualizado y se aplica</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5182,30 +5149,28 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>53</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Hasta 4 NyA por dormitorio</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -5215,17 +5180,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -5235,92 +5200,92 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No cuenta con equipo técnico</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No cuenta con personal de conducción</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -5330,7 +5295,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -5340,13 +5305,13 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -5356,22 +5321,22 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
@@ -5381,137 +5346,135 @@
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1 vez por semana o más</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>1 vez por semana o más</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mitre 4021</t>
+          <t>Sarmiento 593</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>U6582C</t>
+          <t>E4404D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11-4152-5136</t>
+          <t>11-4370-2330</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>para algunos pocos espcios</t>
+          <t>Sí en todos los espacios requeridos</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>46</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Entre 5 y 8 por dormitorio</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -5521,32 +5484,32 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5561,12 +5524,12 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>No cuenta con equipo técnico</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>No cuena con personal de cuidado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -5576,17 +5539,17 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>No cuenta con personal de conducción</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5596,7 +5559,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5606,12 +5569,12 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -5621,22 +5584,22 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5647,7 +5610,7 @@
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -5657,17 +5620,17 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5677,84 +5640,84 @@
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>No realizan esta actividad</t>
+          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Güemes 3819</t>
+          <t>Güemes 4812</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>D4824E</t>
+          <t>Z1339E</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11-4906-4241</t>
+          <t>11-4690-1659</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5764,46 +5727,44 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>para algunos pocos espcios</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
+          <t>1 tablet o computadora por cada 5 NyA o más</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>2007</v>
+        <v>214</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -5812,27 +5773,27 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Aloja niños niñas y adolescentes</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -5842,7 +5803,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5852,12 +5813,12 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -5867,17 +5828,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8 o más personas</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No cuenta con personal de conducción</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5887,12 +5848,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5907,7 +5868,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -5922,7 +5883,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -5932,7 +5893,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -5945,19 +5906,15 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+      <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -5967,7 +5924,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5987,39 +5944,39 @@
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>1 vez por semana o más</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6029,7 +5986,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6039,17 +5996,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mitre 2461</t>
+          <t>Rivadavia 3503</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>S1601H</t>
+          <t>W8736D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11-4190-6153</t>
+          <t>11-4567-3369</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6059,37 +6016,37 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>y no es posible adaptarlos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -6102,52 +6059,50 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="S19" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>9 y más</t>
+          <t>Entre 5 y 8 por dormitorio</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -6157,17 +6112,17 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -6177,17 +6132,17 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>8 o más personas</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -6197,17 +6152,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6217,32 +6172,32 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -6258,17 +6213,17 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6278,44 +6233,44 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
         <is>
           <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6325,32 +6280,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarmiento 4263</t>
+          <t>Belgrano 3458</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>H2143E</t>
+          <t>H2225H</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11-4891-7798</t>
+          <t>11-4900-5342</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6365,27 +6320,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>pero esta en diseño</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -6403,13 +6358,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="S20" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -6423,12 +6376,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -6438,67 +6391,67 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>6 o más personas</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>No cuenta con personal de conducción</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -6508,12 +6461,12 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -6523,62 +6476,58 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Discapacidad</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>No se realiza desde el dispositivo</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -6588,49 +6537,49 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6645,22 +6594,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>San Martín 2791</t>
+          <t>Rivadavia 3864</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Y7226F</t>
+          <t>N1153H</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11-4741-8994</t>
+          <t>11-4394-9955</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -6670,17 +6619,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sí en la mayoría de los espacios</t>
+          <t>aunque se puede adaptar si lo requiere</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -6690,17 +6639,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -6708,17 +6657,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="S21" s="5" t="n">
+        <v>210</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>221</v>
+        <v>484</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Hasta 4 NyA por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -6733,17 +6680,17 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -6758,7 +6705,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -6768,12 +6715,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>No cuenta con equipo técnico</t>
+          <t>6 o más personas</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -6783,27 +6730,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6813,72 +6760,68 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6888,7 +6831,7 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
@@ -6898,44 +6841,44 @@
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No gubernamental</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6945,27 +6888,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Güemes 4058</t>
+          <t>Alberdi 3355</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>E4886G</t>
+          <t>Y6992B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11-4685-6881</t>
+          <t>11-4909-7464</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -6975,32 +6918,32 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sí en todos los espacios requeridos</t>
+          <t>para algunos pocos espcios</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>No cuentan con tablet o computadora para los NyA</t>
+          <t>1 tablet o computadora por cada 5 NyA o más</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -7010,90 +6953,88 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>45</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Hasta 4 NyA por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Aloja niños niñas y adolescentes</t>
+          <t>Aloja solo niños y adolescente varones</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8 o más personas</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -7103,7 +7044,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -7113,12 +7054,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -7128,7 +7069,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -7138,7 +7079,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -7153,12 +7094,12 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -7168,27 +7109,27 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -7203,17 +7144,17 @@
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>1 vez por semana o más</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -7223,7 +7164,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
@@ -7240,49 +7181,49 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No gubernamental</t>
+          <t>Mixta</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Güemes 1948</t>
+          <t>Mitre 3742</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>S6992B</t>
+          <t>M6942B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11-4909-7464</t>
+          <t>11-4802-7018</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>pero esta en diseño</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7300,31 +7241,29 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -7333,17 +7272,17 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -7363,7 +7302,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -7373,37 +7312,37 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>No cuenta con equipo técnico</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>No cuena con personal de cuidado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>8 o más personas</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>3 o más personas</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -7418,7 +7357,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -7428,27 +7367,27 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -7458,37 +7397,33 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>No en ninguna situación</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7498,12 +7433,12 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -7513,7 +7448,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>No realizan esta actividad</t>
+          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
@@ -7523,7 +7458,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>No realizan esta actividad</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -7535,12 +7470,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7550,32 +7485,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Güemes 3071</t>
+          <t>San Martín 3802</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>E7018I</t>
+          <t>X4629J</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11-4760-6876</t>
+          <t>11-4144-9543</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7585,14 +7520,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>pero esta en diseño</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Sí en todos los espacios requeridos</t>
@@ -7605,45 +7540,43 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>223</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>2002</v>
+        <v>219</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Hasta 4 NyA por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -7653,12 +7586,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -7668,47 +7601,47 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8 o más perosnas</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No cuenta con personal de conducción</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -7718,7 +7651,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7728,12 +7661,12 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -7743,7 +7676,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7763,7 +7696,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7774,17 +7707,17 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
+          <t>en todas las situaciones</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
           <t>en algunas situaciones</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>en algunas situaciones</t>
-        </is>
-      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7799,54 +7732,54 @@
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>1 vez por semana o más</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
         <is>
           <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BI24" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No gubernamental</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7856,22 +7789,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Martín 4116</t>
+          <t>Rivadavia 2980</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U2204B</t>
+          <t>E9313D</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11-4429-3430</t>
+          <t>11-4258-8900</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -7881,7 +7814,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>esta actualizado y no se aplica</t>
+          <t>esta actualizado y se aplica</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7896,12 +7829,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -7916,7 +7849,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -7924,13 +7857,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="S25" s="5" t="n">
+        <v>43</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -7939,12 +7870,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -7954,12 +7885,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -7979,27 +7910,27 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -8014,27 +7945,27 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
@@ -8044,22 +7975,22 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -8069,32 +8000,32 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Acompañamiento terapéutico</t>
+          <t>Discapacidad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -8109,7 +8040,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -8119,69 +8050,69 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
           <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alberdi 521</t>
+          <t>Rivadavia 3729</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>P6119F</t>
+          <t>T8957J</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-4206-9313</t>
+          <t>11-4552-7785</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8191,51 +8122,49 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Sí en la mayoría de los espacios</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>45</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -8244,7 +8173,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Aloja solo niñas y adolescentes mujeres</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -8254,17 +8183,17 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -8274,12 +8203,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -8289,27 +8218,27 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>6 o más personas</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -8319,12 +8248,12 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -8334,12 +8263,12 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -8354,7 +8283,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -8364,7 +8293,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -8374,33 +8303,37 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Discapacidad</t>
+        </is>
+      </c>
       <c r="AX26" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
           <t>en todas las situaciones</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>No en ninguna situación</t>
-        </is>
-      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -8410,44 +8343,44 @@
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1 vez por semana o más</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8457,37 +8390,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rivadavia 3729</t>
+          <t>Güemes 3869</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>T8957J</t>
+          <t>R2443G</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11-4552-7785</t>
+          <t>11-4964-2734</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>esta actualizado y no se aplica</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -8497,22 +8430,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>aunque se puede adaptar si lo requiere</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>No cuentan con tablet o computadora para los NyA</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -8527,20 +8460,18 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>211</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>217</v>
+        <v>2004</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Entre 5 y 8 por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -8555,7 +8486,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -8570,12 +8501,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -8590,42 +8521,42 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
+          <t>6 o más personas</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -8635,7 +8566,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -8645,27 +8576,27 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -8680,7 +8611,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Discapacidad</t>
+          <t>Acompañamiento terapéutico</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8690,32 +8621,32 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>No en ninguna situación</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -8730,17 +8661,17 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
         </is>
       </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
@@ -8752,12 +8683,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8767,37 +8698,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mitre 967</t>
+          <t>Mitre 4207</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>M8138J</t>
+          <t>H2013H</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11-4510-9584</t>
+          <t>11-4205-6626</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>pero esta desactualizado</t>
+          <t>esta actualizado y se aplica</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8807,41 +8738,39 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí en la mayoría de los espacios</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
+          <t>1 tablet o computadora por NyA</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>41</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -8850,12 +8779,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Aloja niños niñas y adolescentes</t>
+          <t>Aloja solo niñas y adolescentes mujeres</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -8870,27 +8799,27 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -8900,42 +8829,42 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No cuenta con equipo técnico</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 o más personas</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -8960,22 +8889,22 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8983,11 +8912,7 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Discapacidad</t>
-        </is>
-      </c>
+      <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -9000,27 +8925,27 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -9030,17 +8955,17 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
-        </is>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>Menos de 1 vez en el mes</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -9052,12 +8977,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9072,42 +8997,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rivadavia 2451</t>
+          <t>Rivadavia 1576</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>D2479J</t>
+          <t>L6598H</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11-4708-9307</t>
+          <t>11-4296-4711</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>pero esta desactualizado</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>esta actualizado y se aplica</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -9122,7 +9047,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -9137,16 +9062,14 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -9165,7 +9088,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -9180,17 +9103,17 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -9200,24 +9123,24 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 o más personas</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
+          <t>8 o más perosnas</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AI29" t="inlineStr">
         <is>
           <t>No cuenta con personal de conducción</t>
@@ -9240,17 +9163,17 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
@@ -9260,7 +9183,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -9270,53 +9193,57 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Acompañamiento terapéutico</t>
+        </is>
+      </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>en todas las situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No en ninguna situación</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
@@ -9326,27 +9253,27 @@
       </c>
       <c r="BE29" t="inlineStr">
         <is>
+          <t>No realizan esta actividad</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BI29" t="inlineStr">
-        <is>
-          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
@@ -9358,12 +9285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9373,62 +9300,62 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mitre 1156</t>
+          <t>Sarmiento 1121</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>D6072I</t>
+          <t>P2374C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-4485-6381</t>
+          <t>11-4379-8361</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí en la mayoría de los espacios</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -9438,25 +9365,23 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>33</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>623</v>
+        <v>666</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Hasta 4 NyA por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Aloja solo niñas y adolescentes mujeres</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -9471,57 +9396,57 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>No cuenta con equipo técnico</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8 o más perosnas</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -9531,22 +9456,22 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -9556,12 +9481,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -9571,37 +9496,33 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Acompañamiento terapéutico</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>No se realiza desde el dispositivo</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9611,7 +9532,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9621,37 +9542,37 @@
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BF30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
         <is>
           <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
-        </is>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>No realizan esta actividad</t>
+          <t>Entre 1 y 3 veces por mes</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9589,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Gubernamental</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -9678,27 +9599,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Belgrano 1735</t>
+          <t>Belgrano 4774</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>H5096A</t>
+          <t>T4068B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-4756-8873</t>
+          <t>11-4636-6908</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9708,7 +9629,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9733,7 +9654,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -9743,25 +9664,23 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Hasta 4 NyA por dormitorio</t>
+          <t>Entre 5 y 8 por dormitorio</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Aloja solo niños y adolescente varones</t>
+          <t>Aloja niños niñas y adolescentes</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -9771,12 +9690,12 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -9791,39 +9710,39 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
+          <t>No cuenta con equipo técnico</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AI31" t="inlineStr">
         <is>
           <t>1</t>
@@ -9836,17 +9755,17 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -9861,22 +9780,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
@@ -9886,28 +9805,32 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Acompañamiento terapéutico</t>
+        </is>
+      </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>No en ninguna situación</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -9932,12 +9855,12 @@
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
@@ -9947,12 +9870,12 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
+          <t>Menos de 1 vez en el mes</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
           <t>1 vez por semana o más</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9892,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9979,42 +9902,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mitre 3844</t>
+          <t>Alberdi 2819</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>D2816H</t>
+          <t>N3039F</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11-4711-9782</t>
+          <t>11-4547-7553</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>pero esta en diseño</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>pero esta desactualizado</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -10024,12 +9947,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 2 a 4 NyA</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -10039,7 +9962,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -10047,13 +9970,11 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="S32" s="5" t="n">
+        <v>25</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -10072,7 +9993,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -10097,62 +10018,62 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>No cuena con personal de cuidado</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>No cuenta con personal de apoyo</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No cuenta con personal de conducción</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -10167,7 +10088,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -10177,48 +10098,48 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>No se realiza desde el dispositivo</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>en todas las situaciones</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>en la mayoría de las situaciones</t>
+          <t>en algunas situaciones</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -10228,7 +10149,7 @@
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -10238,79 +10159,79 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Entre 1 y 3 veces por mes</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
           <t>No realizan esta actividad</t>
         </is>
       </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>No realizan esta actividad</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>1 vez por semana o más</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gubernamental</t>
+          <t>No gubernamental</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Belgrano 443</t>
+          <t>Sarmiento 365</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Q6080I</t>
+          <t>H8371F</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11-4507-9897</t>
+          <t>11-4480-8273</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>esta actualizado y se aplica</t>
+          <t>esta actualizado y no se aplica</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -10320,12 +10241,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sí en la mayoría de los espacios</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1 tablet o computadora por cada 5 NyA o más</t>
+          <t>No cuentan con tablet o computadora para los NyA</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -10335,70 +10256,68 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>201</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>2006</v>
+        <v>9</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Entre 5 y 8 por dormitorio</t>
+          <t>9 y más</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Aloja niños niñas y adolescentes</t>
+          <t>Aloja solo niños y adolescente varones</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -10408,22 +10327,22 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 o más personas</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -10433,17 +10352,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -10453,12 +10372,12 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
@@ -10468,32 +10387,32 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr"/>
@@ -10509,17 +10428,17 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>en algunas situaciones</t>
+          <t>en la mayoría de las situaciones</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -10539,533 +10458,703 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
+          <t>1 vez por semana o más</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
           <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>Entre 1 y 3 veces por mes</t>
-        </is>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>1 vez por semana o más</t>
+          <t>Menos de 1 vez en el mes</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Entre 1 y 3 veces por mes</t>
+          <t>No realizan esta actividad</t>
         </is>
       </c>
     </row>
     <row r="34">
+      <c r="S34" s="5" t="n"/>
       <c r="T34" s="5" t="n"/>
     </row>
     <row r="35">
+      <c r="S35" s="5" t="n"/>
       <c r="T35" s="5" t="n"/>
     </row>
     <row r="36">
+      <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
     </row>
     <row r="37">
+      <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
     </row>
     <row r="38">
+      <c r="S38" s="5" t="n"/>
       <c r="T38" s="5" t="n"/>
     </row>
     <row r="39">
+      <c r="S39" s="5" t="n"/>
       <c r="T39" s="5" t="n"/>
     </row>
     <row r="40">
+      <c r="S40" s="5" t="n"/>
       <c r="T40" s="5" t="n"/>
     </row>
     <row r="41">
+      <c r="S41" s="5" t="n"/>
       <c r="T41" s="5" t="n"/>
     </row>
     <row r="42">
+      <c r="S42" s="5" t="n"/>
       <c r="T42" s="5" t="n"/>
     </row>
     <row r="43">
+      <c r="S43" s="5" t="n"/>
       <c r="T43" s="5" t="n"/>
     </row>
     <row r="44">
+      <c r="S44" s="5" t="n"/>
       <c r="T44" s="5" t="n"/>
     </row>
     <row r="45">
+      <c r="S45" s="5" t="n"/>
       <c r="T45" s="5" t="n"/>
     </row>
     <row r="46">
+      <c r="S46" s="5" t="n"/>
       <c r="T46" s="5" t="n"/>
     </row>
     <row r="47">
+      <c r="S47" s="5" t="n"/>
       <c r="T47" s="5" t="n"/>
     </row>
     <row r="48">
+      <c r="S48" s="5" t="n"/>
       <c r="T48" s="5" t="n"/>
     </row>
     <row r="49">
+      <c r="S49" s="5" t="n"/>
       <c r="T49" s="5" t="n"/>
     </row>
     <row r="50">
+      <c r="S50" s="5" t="n"/>
       <c r="T50" s="5" t="n"/>
     </row>
     <row r="51">
+      <c r="S51" s="5" t="n"/>
       <c r="T51" s="5" t="n"/>
     </row>
     <row r="52">
+      <c r="S52" s="5" t="n"/>
       <c r="T52" s="5" t="n"/>
     </row>
     <row r="53">
+      <c r="S53" s="5" t="n"/>
       <c r="T53" s="5" t="n"/>
     </row>
     <row r="54">
+      <c r="S54" s="5" t="n"/>
       <c r="T54" s="5" t="n"/>
     </row>
     <row r="55">
+      <c r="S55" s="5" t="n"/>
       <c r="T55" s="5" t="n"/>
     </row>
     <row r="56">
+      <c r="S56" s="5" t="n"/>
       <c r="T56" s="5" t="n"/>
     </row>
     <row r="57">
+      <c r="S57" s="5" t="n"/>
       <c r="T57" s="5" t="n"/>
     </row>
     <row r="58">
+      <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
     </row>
     <row r="59">
+      <c r="S59" s="5" t="n"/>
       <c r="T59" s="5" t="n"/>
     </row>
     <row r="60">
+      <c r="S60" s="5" t="n"/>
       <c r="T60" s="5" t="n"/>
     </row>
     <row r="61">
+      <c r="S61" s="5" t="n"/>
       <c r="T61" s="5" t="n"/>
     </row>
     <row r="62">
+      <c r="S62" s="5" t="n"/>
       <c r="T62" s="5" t="n"/>
     </row>
     <row r="63">
+      <c r="S63" s="5" t="n"/>
       <c r="T63" s="5" t="n"/>
     </row>
     <row r="64">
+      <c r="S64" s="5" t="n"/>
       <c r="T64" s="5" t="n"/>
     </row>
     <row r="65">
+      <c r="S65" s="5" t="n"/>
       <c r="T65" s="5" t="n"/>
     </row>
     <row r="66">
+      <c r="S66" s="5" t="n"/>
       <c r="T66" s="5" t="n"/>
     </row>
     <row r="67">
+      <c r="S67" s="5" t="n"/>
       <c r="T67" s="5" t="n"/>
     </row>
     <row r="68">
+      <c r="S68" s="5" t="n"/>
       <c r="T68" s="5" t="n"/>
     </row>
     <row r="69">
+      <c r="S69" s="5" t="n"/>
       <c r="T69" s="5" t="n"/>
     </row>
     <row r="70">
+      <c r="S70" s="5" t="n"/>
       <c r="T70" s="5" t="n"/>
     </row>
     <row r="71">
+      <c r="S71" s="5" t="n"/>
       <c r="T71" s="5" t="n"/>
     </row>
     <row r="72">
+      <c r="S72" s="5" t="n"/>
       <c r="T72" s="5" t="n"/>
     </row>
     <row r="73">
+      <c r="S73" s="5" t="n"/>
       <c r="T73" s="5" t="n"/>
     </row>
     <row r="74">
+      <c r="S74" s="5" t="n"/>
       <c r="T74" s="5" t="n"/>
     </row>
     <row r="75">
+      <c r="S75" s="5" t="n"/>
       <c r="T75" s="5" t="n"/>
     </row>
     <row r="76">
+      <c r="S76" s="5" t="n"/>
       <c r="T76" s="5" t="n"/>
     </row>
     <row r="77">
+      <c r="S77" s="5" t="n"/>
       <c r="T77" s="5" t="n"/>
     </row>
     <row r="78">
+      <c r="S78" s="5" t="n"/>
       <c r="T78" s="5" t="n"/>
     </row>
     <row r="79">
+      <c r="S79" s="5" t="n"/>
       <c r="T79" s="5" t="n"/>
     </row>
     <row r="80">
+      <c r="S80" s="5" t="n"/>
       <c r="T80" s="5" t="n"/>
     </row>
     <row r="81">
+      <c r="S81" s="5" t="n"/>
       <c r="T81" s="5" t="n"/>
     </row>
     <row r="82">
+      <c r="S82" s="5" t="n"/>
       <c r="T82" s="5" t="n"/>
     </row>
     <row r="83">
+      <c r="S83" s="5" t="n"/>
       <c r="T83" s="5" t="n"/>
     </row>
     <row r="84">
+      <c r="S84" s="5" t="n"/>
       <c r="T84" s="5" t="n"/>
     </row>
     <row r="85">
+      <c r="S85" s="5" t="n"/>
       <c r="T85" s="5" t="n"/>
     </row>
     <row r="86">
+      <c r="S86" s="5" t="n"/>
       <c r="T86" s="5" t="n"/>
     </row>
     <row r="87">
+      <c r="S87" s="5" t="n"/>
       <c r="T87" s="5" t="n"/>
     </row>
     <row r="88">
+      <c r="S88" s="5" t="n"/>
       <c r="T88" s="5" t="n"/>
     </row>
     <row r="89">
+      <c r="S89" s="5" t="n"/>
       <c r="T89" s="5" t="n"/>
     </row>
     <row r="90">
+      <c r="S90" s="5" t="n"/>
       <c r="T90" s="5" t="n"/>
     </row>
     <row r="91">
+      <c r="S91" s="5" t="n"/>
       <c r="T91" s="5" t="n"/>
     </row>
     <row r="92">
+      <c r="S92" s="5" t="n"/>
       <c r="T92" s="5" t="n"/>
     </row>
     <row r="93">
+      <c r="S93" s="5" t="n"/>
       <c r="T93" s="5" t="n"/>
     </row>
     <row r="94">
+      <c r="S94" s="5" t="n"/>
       <c r="T94" s="5" t="n"/>
     </row>
     <row r="95">
+      <c r="S95" s="5" t="n"/>
       <c r="T95" s="5" t="n"/>
     </row>
     <row r="96">
+      <c r="S96" s="5" t="n"/>
       <c r="T96" s="5" t="n"/>
     </row>
     <row r="97">
+      <c r="S97" s="5" t="n"/>
       <c r="T97" s="5" t="n"/>
     </row>
     <row r="98">
+      <c r="S98" s="5" t="n"/>
       <c r="T98" s="5" t="n"/>
     </row>
     <row r="99">
+      <c r="S99" s="5" t="n"/>
       <c r="T99" s="5" t="n"/>
     </row>
     <row r="100">
+      <c r="S100" s="5" t="n"/>
       <c r="T100" s="5" t="n"/>
     </row>
     <row r="101">
+      <c r="S101" s="5" t="n"/>
       <c r="T101" s="5" t="n"/>
     </row>
     <row r="102">
+      <c r="S102" s="5" t="n"/>
       <c r="T102" s="5" t="n"/>
     </row>
     <row r="103">
+      <c r="S103" s="5" t="n"/>
       <c r="T103" s="5" t="n"/>
     </row>
     <row r="104">
+      <c r="S104" s="5" t="n"/>
       <c r="T104" s="5" t="n"/>
     </row>
     <row r="105">
+      <c r="S105" s="5" t="n"/>
       <c r="T105" s="5" t="n"/>
     </row>
     <row r="106">
+      <c r="S106" s="5" t="n"/>
       <c r="T106" s="5" t="n"/>
     </row>
     <row r="107">
+      <c r="S107" s="5" t="n"/>
       <c r="T107" s="5" t="n"/>
     </row>
     <row r="108">
+      <c r="S108" s="5" t="n"/>
       <c r="T108" s="5" t="n"/>
     </row>
     <row r="109">
+      <c r="S109" s="5" t="n"/>
       <c r="T109" s="5" t="n"/>
     </row>
     <row r="110">
+      <c r="S110" s="5" t="n"/>
       <c r="T110" s="5" t="n"/>
     </row>
     <row r="111">
+      <c r="S111" s="5" t="n"/>
       <c r="T111" s="5" t="n"/>
     </row>
     <row r="112">
+      <c r="S112" s="5" t="n"/>
       <c r="T112" s="5" t="n"/>
     </row>
     <row r="113">
+      <c r="S113" s="5" t="n"/>
       <c r="T113" s="5" t="n"/>
     </row>
     <row r="114">
+      <c r="S114" s="5" t="n"/>
       <c r="T114" s="5" t="n"/>
     </row>
     <row r="115">
+      <c r="S115" s="5" t="n"/>
       <c r="T115" s="5" t="n"/>
     </row>
     <row r="116">
+      <c r="S116" s="5" t="n"/>
       <c r="T116" s="5" t="n"/>
     </row>
     <row r="117">
+      <c r="S117" s="5" t="n"/>
       <c r="T117" s="5" t="n"/>
     </row>
     <row r="118">
+      <c r="S118" s="5" t="n"/>
       <c r="T118" s="5" t="n"/>
     </row>
     <row r="119">
+      <c r="S119" s="5" t="n"/>
       <c r="T119" s="5" t="n"/>
     </row>
     <row r="120">
+      <c r="S120" s="5" t="n"/>
       <c r="T120" s="5" t="n"/>
     </row>
     <row r="121">
+      <c r="S121" s="5" t="n"/>
       <c r="T121" s="5" t="n"/>
     </row>
     <row r="122">
+      <c r="S122" s="5" t="n"/>
       <c r="T122" s="5" t="n"/>
     </row>
     <row r="123">
+      <c r="S123" s="5" t="n"/>
       <c r="T123" s="5" t="n"/>
     </row>
     <row r="124">
+      <c r="S124" s="5" t="n"/>
       <c r="T124" s="5" t="n"/>
     </row>
     <row r="125">
+      <c r="S125" s="5" t="n"/>
       <c r="T125" s="5" t="n"/>
     </row>
     <row r="126">
+      <c r="S126" s="5" t="n"/>
       <c r="T126" s="5" t="n"/>
     </row>
     <row r="127">
+      <c r="S127" s="5" t="n"/>
       <c r="T127" s="5" t="n"/>
     </row>
     <row r="128">
+      <c r="S128" s="5" t="n"/>
       <c r="T128" s="5" t="n"/>
     </row>
     <row r="129">
+      <c r="S129" s="5" t="n"/>
       <c r="T129" s="5" t="n"/>
     </row>
     <row r="130">
+      <c r="S130" s="5" t="n"/>
       <c r="T130" s="5" t="n"/>
     </row>
     <row r="131">
+      <c r="S131" s="5" t="n"/>
       <c r="T131" s="5" t="n"/>
     </row>
     <row r="132">
+      <c r="S132" s="5" t="n"/>
       <c r="T132" s="5" t="n"/>
     </row>
     <row r="133">
+      <c r="S133" s="5" t="n"/>
       <c r="T133" s="5" t="n"/>
     </row>
     <row r="134">
+      <c r="S134" s="5" t="n"/>
       <c r="T134" s="5" t="n"/>
     </row>
     <row r="135">
+      <c r="S135" s="5" t="n"/>
       <c r="T135" s="5" t="n"/>
     </row>
     <row r="136">
+      <c r="S136" s="5" t="n"/>
       <c r="T136" s="5" t="n"/>
     </row>
     <row r="137">
+      <c r="S137" s="5" t="n"/>
       <c r="T137" s="5" t="n"/>
     </row>
     <row r="138">
+      <c r="S138" s="5" t="n"/>
       <c r="T138" s="5" t="n"/>
     </row>
     <row r="139">
+      <c r="S139" s="5" t="n"/>
       <c r="T139" s="5" t="n"/>
     </row>
     <row r="140">
+      <c r="S140" s="5" t="n"/>
       <c r="T140" s="5" t="n"/>
     </row>
     <row r="141">
+      <c r="S141" s="5" t="n"/>
       <c r="T141" s="5" t="n"/>
     </row>
     <row r="142">
+      <c r="S142" s="5" t="n"/>
       <c r="T142" s="5" t="n"/>
     </row>
     <row r="143">
+      <c r="S143" s="5" t="n"/>
       <c r="T143" s="5" t="n"/>
     </row>
     <row r="144">
+      <c r="S144" s="5" t="n"/>
       <c r="T144" s="5" t="n"/>
     </row>
     <row r="145">
+      <c r="S145" s="5" t="n"/>
       <c r="T145" s="5" t="n"/>
     </row>
     <row r="146">
+      <c r="S146" s="5" t="n"/>
       <c r="T146" s="5" t="n"/>
     </row>
     <row r="147">
+      <c r="S147" s="5" t="n"/>
       <c r="T147" s="5" t="n"/>
     </row>
     <row r="148">
+      <c r="S148" s="5" t="n"/>
       <c r="T148" s="5" t="n"/>
     </row>
     <row r="149">
+      <c r="S149" s="5" t="n"/>
       <c r="T149" s="5" t="n"/>
     </row>
     <row r="150">
+      <c r="S150" s="5" t="n"/>
       <c r="T150" s="5" t="n"/>
     </row>
     <row r="151">
+      <c r="S151" s="5" t="n"/>
       <c r="T151" s="5" t="n"/>
     </row>
     <row r="152">
+      <c r="S152" s="5" t="n"/>
       <c r="T152" s="5" t="n"/>
     </row>
     <row r="153">
+      <c r="S153" s="5" t="n"/>
       <c r="T153" s="5" t="n"/>
     </row>
     <row r="154">
+      <c r="S154" s="5" t="n"/>
       <c r="T154" s="5" t="n"/>
     </row>
     <row r="155">
+      <c r="S155" s="5" t="n"/>
       <c r="T155" s="5" t="n"/>
     </row>
     <row r="156">
+      <c r="S156" s="5" t="n"/>
       <c r="T156" s="5" t="n"/>
     </row>
     <row r="157">
+      <c r="S157" s="5" t="n"/>
       <c r="T157" s="5" t="n"/>
     </row>
     <row r="158">
+      <c r="S158" s="5" t="n"/>
       <c r="T158" s="5" t="n"/>
     </row>
     <row r="159">
+      <c r="S159" s="5" t="n"/>
       <c r="T159" s="5" t="n"/>
     </row>
     <row r="160">
+      <c r="S160" s="5" t="n"/>
       <c r="T160" s="5" t="n"/>
     </row>
     <row r="161">
+      <c r="S161" s="5" t="n"/>
       <c r="T161" s="5" t="n"/>
     </row>
     <row r="162">
+      <c r="S162" s="5" t="n"/>
       <c r="T162" s="5" t="n"/>
     </row>
     <row r="163">
+      <c r="S163" s="5" t="n"/>
       <c r="T163" s="5" t="n"/>
     </row>
     <row r="164">
+      <c r="S164" s="5" t="n"/>
       <c r="T164" s="5" t="n"/>
     </row>
     <row r="165">
+      <c r="S165" s="5" t="n"/>
       <c r="T165" s="5" t="n"/>
     </row>
     <row r="166">
+      <c r="S166" s="5" t="n"/>
       <c r="T166" s="5" t="n"/>
     </row>
     <row r="167">
+      <c r="S167" s="5" t="n"/>
       <c r="T167" s="5" t="n"/>
     </row>
     <row r="168">
+      <c r="S168" s="5" t="n"/>
       <c r="T168" s="5" t="n"/>
     </row>
     <row r="169">
+      <c r="S169" s="5" t="n"/>
       <c r="T169" s="5" t="n"/>
     </row>
     <row r="170">
+      <c r="S170" s="5" t="n"/>
       <c r="T170" s="5" t="n"/>
     </row>
     <row r="171">
+      <c r="S171" s="5" t="n"/>
       <c r="T171" s="5" t="n"/>
     </row>
     <row r="172">
+      <c r="S172" s="5" t="n"/>
       <c r="T172" s="5" t="n"/>
     </row>
     <row r="173">
+      <c r="S173" s="5" t="n"/>
       <c r="T173" s="5" t="n"/>
     </row>
     <row r="174">
+      <c r="S174" s="5" t="n"/>
       <c r="T174" s="5" t="n"/>
     </row>
     <row r="175">
+      <c r="S175" s="5" t="n"/>
       <c r="T175" s="5" t="n"/>
     </row>
     <row r="176">
+      <c r="S176" s="5" t="n"/>
       <c r="T176" s="5" t="n"/>
     </row>
     <row r="177">
+      <c r="S177" s="5" t="n"/>
       <c r="T177" s="5" t="n"/>
     </row>
     <row r="178">
+      <c r="S178" s="5" t="n"/>
       <c r="T178" s="5" t="n"/>
     </row>
     <row r="179">
+      <c r="S179" s="5" t="n"/>
       <c r="T179" s="5" t="n"/>
     </row>
     <row r="180">
+      <c r="S180" s="5" t="n"/>
       <c r="T180" s="5" t="n"/>
     </row>
     <row r="181">
+      <c r="S181" s="5" t="n"/>
       <c r="T181" s="5" t="n"/>
     </row>
     <row r="182">
+      <c r="S182" s="5" t="n"/>
       <c r="T182" s="5" t="n"/>
     </row>
     <row r="183">
+      <c r="S183" s="5" t="n"/>
       <c r="T183" s="5" t="n"/>
     </row>
     <row r="184">
+      <c r="S184" s="5" t="n"/>
       <c r="T184" s="5" t="n"/>
     </row>
     <row r="185">
+      <c r="S185" s="5" t="n"/>
       <c r="T185" s="5" t="n"/>
     </row>
     <row r="186">
+      <c r="S186" s="5" t="n"/>
       <c r="T186" s="5" t="n"/>
     </row>
     <row r="187">
+      <c r="S187" s="5" t="n"/>
       <c r="T187" s="5" t="n"/>
     </row>
     <row r="188">
+      <c r="S188" s="5" t="n"/>
       <c r="T188" s="5" t="n"/>
     </row>
     <row r="189">
+      <c r="S189" s="5" t="n"/>
       <c r="T189" s="5" t="n"/>
     </row>
     <row r="190">
+      <c r="S190" s="5" t="n"/>
       <c r="T190" s="5" t="n"/>
     </row>
     <row r="191">
+      <c r="S191" s="5" t="n"/>
       <c r="T191" s="5" t="n"/>
     </row>
     <row r="192">
+      <c r="S192" s="5" t="n"/>
       <c r="T192" s="5" t="n"/>
     </row>
     <row r="193">
+      <c r="S193" s="5" t="n"/>
       <c r="T193" s="5" t="n"/>
     </row>
     <row r="194">
+      <c r="S194" s="5" t="n"/>
       <c r="T194" s="5" t="n"/>
     </row>
     <row r="195">
+      <c r="S195" s="5" t="n"/>
       <c r="T195" s="5" t="n"/>
     </row>
     <row r="196">
+      <c r="S196" s="5" t="n"/>
       <c r="T196" s="5" t="n"/>
     </row>
     <row r="197">
+      <c r="S197" s="5" t="n"/>
       <c r="T197" s="5" t="n"/>
     </row>
     <row r="198">
+      <c r="S198" s="5" t="n"/>
       <c r="T198" s="5" t="n"/>
     </row>
     <row r="199">
+      <c r="S199" s="5" t="n"/>
       <c r="T199" s="5" t="n"/>
     </row>
     <row r="200">
+      <c r="S200" s="5" t="n"/>
       <c r="T200" s="5" t="n"/>
     </row>
     <row r="201">
+      <c r="S201" s="5" t="n"/>
       <c r="T201" s="5" t="n"/>
     </row>
     <row r="202">
+      <c r="S202" s="5" t="n"/>
       <c r="T202" s="5" t="n"/>
     </row>
     <row r="203">
+      <c r="S203" s="5" t="n"/>
       <c r="T203" s="5" t="n"/>
     </row>
   </sheetData>
@@ -12587,7 +12676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12629,7 +12718,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+          <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -12649,7 +12738,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+          <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12665,7 +12754,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -12685,11 +12774,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+          <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12705,7 +12794,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -12725,11 +12814,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+          <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12745,7 +12834,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -12765,11 +12854,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+          <t>Capacidad de alojamiento (Plazas)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12785,7 +12874,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -12805,14 +12894,154 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Capacidad de alojamiento (Plazas)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>24</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Capacidad de alojamiento (Plazas)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>27</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Capacidad de alojamiento (Plazas)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>27</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rango_alojados</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M Residencial</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>33</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Capacidad de alojamiento (Plazas)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>rango_alojados</t>
         </is>
